--- a/scripts/out_syscohada/grandlivre_ci.xlsx
+++ b/scripts/out_syscohada/grandlivre_ci.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="130">
   <si>
     <t>YAHRIA BUSINESS OS — ÉTATS FINANCIERS SYSCOHADA (SYSTÈME NORMAL)</t>
   </si>
@@ -166,12 +166,135 @@
     <t>SD</t>
   </si>
   <si>
+    <t>Compte 4221 — Personnel, rémunérations dues   [Classe 4]</t>
+  </si>
+  <si>
+    <t>31/08/2026</t>
+  </si>
+  <si>
+    <t>PAIE</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857/P1</t>
+  </si>
+  <si>
+    <t>Paie août 2026 — Awa Koné (constatation)</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857/P2</t>
+  </si>
+  <si>
+    <t>Paie août 2026 — Ibrahim Coulibaly (constatation)</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857/P3</t>
+  </si>
+  <si>
+    <t>Paie août 2026 — Fatou Diomandé (constatation)</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857/P4</t>
+  </si>
+  <si>
+    <t>Paie août 2026 — Yao Kouassi (constatation)</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857/P5</t>
+  </si>
+  <si>
+    <t>Paie août 2026 — Mariam Sylla (constatation)</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857/P6</t>
+  </si>
+  <si>
+    <t>Paie août 2026 — Jean-Marc Behanzin (constatation)</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857/BQ</t>
+  </si>
+  <si>
+    <t>Paie août 2026 — paiement des salaires (virement, 6 bénéficiaires)</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857-R2/P1</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857-R2/P2</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857-R2/P3</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857-R2/P4</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857-R2/P5</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857-R2/P6</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857-R2/BQ</t>
+  </si>
+  <si>
+    <t>15/09/2026</t>
+  </si>
+  <si>
+    <t>PAIE-REV-2026-08-CMU0C857/P1</t>
+  </si>
+  <si>
+    <t>Contre-passation PAIE-2026-08-CMU0C857 — Awa Koné (extourne constatation)</t>
+  </si>
+  <si>
+    <t>PAIE-REV-2026-08-CMU0C857/P2</t>
+  </si>
+  <si>
+    <t>Contre-passation PAIE-2026-08-CMU0C857 — Ibrahim Coulibaly (extourne constatation)</t>
+  </si>
+  <si>
+    <t>PAIE-REV-2026-08-CMU0C857/P3</t>
+  </si>
+  <si>
+    <t>Contre-passation PAIE-2026-08-CMU0C857 — Fatou Diomandé (extourne constatation)</t>
+  </si>
+  <si>
+    <t>PAIE-REV-2026-08-CMU0C857/P4</t>
+  </si>
+  <si>
+    <t>Contre-passation PAIE-2026-08-CMU0C857 — Yao Kouassi (extourne constatation)</t>
+  </si>
+  <si>
+    <t>PAIE-REV-2026-08-CMU0C857/P5</t>
+  </si>
+  <si>
+    <t>Contre-passation PAIE-2026-08-CMU0C857 — Mariam Sylla (extourne constatation)</t>
+  </si>
+  <si>
+    <t>PAIE-REV-2026-08-CMU0C857/P6</t>
+  </si>
+  <si>
+    <t>Contre-passation PAIE-2026-08-CMU0C857 — Jean-Marc Behanzin (extourne constatation)</t>
+  </si>
+  <si>
+    <t>PAIE-REV-2026-08-CMU0C857/BQ</t>
+  </si>
+  <si>
+    <t>Contre-passation PAIE-2026-08-CMU0C857 — extourne du paiement des salaires (virement)</t>
+  </si>
+  <si>
+    <t>Compte 4311 — Sécurité sociale   [Classe 4]</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>Compte 4321 — État, impôts sur les rémunérations   [Classe 4]</t>
+  </si>
+  <si>
     <t>Compte 4431 — État - TVA collectée   [Classe 4]</t>
   </si>
   <si>
-    <t>SC</t>
-  </si>
-  <si>
     <t>Compte 4452 — État - TVA récupérable   [Classe 4]</t>
   </si>
   <si>
@@ -229,15 +352,15 @@
     <t>05/09/2026</t>
   </si>
   <si>
-    <t>PAIE</t>
-  </si>
-  <si>
     <t>PAIE/2026-09-05</t>
   </si>
   <si>
     <t>Masse salariale mensuelle</t>
   </si>
   <si>
+    <t>Compte 5211 — Banques   [Classe 5]</t>
+  </si>
+  <si>
     <t>Compte 5212 — Compte Wave   [Classe 5]</t>
   </si>
   <si>
@@ -257,6 +380,18 @@
   </si>
   <si>
     <t>Compte 64 — Charges de personnel   [Classe 6]</t>
+  </si>
+  <si>
+    <t>Compte 6611 — Salaires des ouvriers   [Classe 6]</t>
+  </si>
+  <si>
+    <t>Compte 6612 — Salaires des employés   [Classe 6]</t>
+  </si>
+  <si>
+    <t>Compte 6613 — Salaires des chefs d’exploitation et de main-d’œuvre   [Classe 6]</t>
+  </si>
+  <si>
+    <t>Compte 6641 — Cotisations sociales patronales   [Classe 6]</t>
   </si>
   <si>
     <t>Compte 701 — Ventes de produits finis   [Classe 7]</t>
@@ -720,7 +855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:H237"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1131,47 +1266,49 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7">
-        <v>-565200</v>
-      </c>
-      <c r="H22" s="6" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8">
+        <v>1035990</v>
+      </c>
+      <c r="G22" s="8">
+        <v>-1035990</v>
+      </c>
+      <c r="H22" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="8">
-        <v>162000</v>
+        <v>747055</v>
       </c>
       <c r="G23" s="8">
-        <v>-727200</v>
+        <v>-1783045</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -1179,47 +1316,47 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="D24" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="8">
-        <v>67500</v>
+        <v>494065</v>
       </c>
       <c r="G24" s="8">
-        <v>-794700</v>
+        <v>-2277110</v>
       </c>
       <c r="H24" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="E25" s="8"/>
       <c r="F25" s="8">
-        <v>88200</v>
+        <v>381613</v>
       </c>
       <c r="G25" s="8">
-        <v>-882900</v>
+        <v>-2658723</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -1227,23 +1364,23 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="D26" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8">
-        <v>131400</v>
+        <v>435022</v>
       </c>
       <c r="G26" s="8">
-        <v>-1014300</v>
+        <v>-3093745</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -1251,111 +1388,143 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="B27" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="D27" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="E27" s="8"/>
       <c r="F27" s="8">
-        <v>141120</v>
+        <v>662725</v>
       </c>
       <c r="G27" s="8">
-        <v>-1155420</v>
+        <v>-3756470</v>
       </c>
       <c r="H27" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E28" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" s="8">
+        <v>3756470</v>
+      </c>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8">
         <v>0</v>
       </c>
-      <c r="F28" s="12">
-        <v>590220</v>
-      </c>
-      <c r="G28" s="12">
-        <v>-1155420</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>52</v>
+      <c r="H28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" t="s">
+        <v>55</v>
+      </c>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8">
+        <v>1035990</v>
+      </c>
+      <c r="G29" s="8">
+        <v>-1035990</v>
+      </c>
+      <c r="H29" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
+      <c r="A30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" t="s">
+        <v>69</v>
+      </c>
+      <c r="D30" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8">
+        <v>747055</v>
+      </c>
+      <c r="G30" s="8">
+        <v>-1783045</v>
+      </c>
+      <c r="H30" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>11</v>
+      <c r="A31" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31" t="s">
+        <v>59</v>
+      </c>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8">
+        <v>494065</v>
+      </c>
+      <c r="G31" s="8">
+        <v>-2277110</v>
+      </c>
+      <c r="H31" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B32" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C32" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="D32" t="s">
-        <v>57</v>
-      </c>
-      <c r="E32" s="8">
-        <v>133200</v>
-      </c>
-      <c r="F32" s="8"/>
+        <v>61</v>
+      </c>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8">
+        <v>381613</v>
+      </c>
       <c r="G32" s="8">
-        <v>133200</v>
+        <v>-2658723</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -1363,23 +1532,23 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D33" t="s">
-        <v>60</v>
-      </c>
-      <c r="E33" s="8">
-        <v>111600</v>
-      </c>
-      <c r="F33" s="8"/>
+        <v>63</v>
+      </c>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8">
+        <v>435022</v>
+      </c>
       <c r="G33" s="8">
-        <v>244800</v>
+        <v>-3093745</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -1387,23 +1556,23 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B34" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C34" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D34" t="s">
-        <v>63</v>
-      </c>
-      <c r="E34" s="8">
-        <v>69300</v>
-      </c>
-      <c r="F34" s="8"/>
+        <v>65</v>
+      </c>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8">
+        <v>662725</v>
+      </c>
       <c r="G34" s="8">
-        <v>314100</v>
+        <v>-3756470</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -1411,23 +1580,23 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C35" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E35" s="8">
-        <v>171000</v>
+        <v>3756470</v>
       </c>
       <c r="F35" s="8"/>
       <c r="G35" s="8">
-        <v>485100</v>
+        <v>0</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -1435,111 +1604,143 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C36" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D36" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E36" s="8">
-        <v>450000</v>
+        <v>1035990</v>
       </c>
       <c r="F36" s="8"/>
       <c r="G36" s="8">
-        <v>935100</v>
+        <v>1035990</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E37" s="12">
-        <v>935100</v>
-      </c>
-      <c r="F37" s="12">
-        <v>0</v>
-      </c>
-      <c r="G37" s="12">
-        <v>935100</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>50</v>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" t="s">
+        <v>79</v>
+      </c>
+      <c r="E37" s="8">
+        <v>747055</v>
+      </c>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8">
+        <v>1783045</v>
+      </c>
+      <c r="H37" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" t="s">
+        <v>80</v>
+      </c>
+      <c r="D38" t="s">
+        <v>81</v>
+      </c>
+      <c r="E38" s="8">
+        <v>494065</v>
+      </c>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8">
+        <v>2277110</v>
+      </c>
+      <c r="H38" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
+      <c r="A39" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" t="s">
+        <v>83</v>
+      </c>
+      <c r="E39" s="8">
+        <v>381613</v>
+      </c>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8">
+        <v>2658723</v>
+      </c>
+      <c r="H39" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>11</v>
+      <c r="A40" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" t="s">
+        <v>84</v>
+      </c>
+      <c r="D40" t="s">
+        <v>85</v>
+      </c>
+      <c r="E40" s="8">
+        <v>435022</v>
+      </c>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8">
+        <v>3093745</v>
+      </c>
+      <c r="H40" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="B41" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="D41" t="s">
-        <v>57</v>
-      </c>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8">
-        <v>873200</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="E41" s="8">
+        <v>662725</v>
+      </c>
+      <c r="F41" s="8"/>
       <c r="G41" s="8">
-        <v>-873200</v>
+        <v>3756470</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -1547,1053 +1748,1241 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="B42" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C42" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="D42" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="E42" s="8"/>
       <c r="F42" s="8">
-        <v>731600</v>
+        <v>3756470</v>
       </c>
       <c r="G42" s="8">
-        <v>-1604800</v>
+        <v>0</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>61</v>
-      </c>
-      <c r="B43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" t="s">
-        <v>62</v>
-      </c>
-      <c r="D43" t="s">
-        <v>63</v>
-      </c>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8">
-        <v>454300</v>
-      </c>
-      <c r="G43" s="8">
-        <v>-2059100</v>
-      </c>
-      <c r="H43" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>64</v>
-      </c>
-      <c r="B44" t="s">
-        <v>55</v>
-      </c>
-      <c r="C44" t="s">
-        <v>65</v>
-      </c>
-      <c r="D44" t="s">
-        <v>66</v>
-      </c>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8">
-        <v>1121000</v>
-      </c>
-      <c r="G44" s="8">
-        <v>-3180100</v>
-      </c>
-      <c r="H44" t="s">
-        <v>15</v>
+    <row r="43" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E43" s="12">
+        <v>11269410</v>
+      </c>
+      <c r="F43" s="12">
+        <v>11269410</v>
+      </c>
+      <c r="G43" s="12">
+        <v>0</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B45" t="s">
-        <v>72</v>
-      </c>
-      <c r="C45" t="s">
-        <v>73</v>
-      </c>
-      <c r="D45" t="s">
-        <v>74</v>
-      </c>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8">
-        <v>4250000</v>
-      </c>
-      <c r="G45" s="8">
-        <v>-7430100</v>
-      </c>
-      <c r="H45" t="s">
-        <v>15</v>
-      </c>
+      <c r="A45" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>67</v>
-      </c>
-      <c r="B46" t="s">
-        <v>55</v>
-      </c>
-      <c r="C46" t="s">
-        <v>68</v>
-      </c>
-      <c r="D46" t="s">
-        <v>69</v>
-      </c>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8">
-        <v>2950000</v>
-      </c>
-      <c r="G46" s="8">
-        <v>-10380100</v>
-      </c>
-      <c r="H46" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>34</v>
-      </c>
-      <c r="B47" t="s">
-        <v>35</v>
-      </c>
-      <c r="C47" t="s">
-        <v>36</v>
-      </c>
-      <c r="D47" t="s">
-        <v>37</v>
-      </c>
-      <c r="E47" s="8">
-        <v>365800</v>
-      </c>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8">
-        <v>-10014300</v>
-      </c>
-      <c r="H47" t="s">
-        <v>38</v>
+      <c r="A46" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7">
+        <v>-799000</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="B48" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C48" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D48" t="s">
-        <v>46</v>
-      </c>
-      <c r="E48" s="8">
-        <v>442500</v>
-      </c>
-      <c r="F48" s="8"/>
+        <v>55</v>
+      </c>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8">
+        <v>225600</v>
+      </c>
       <c r="G48" s="8">
-        <v>-9571800</v>
+        <v>-1024600</v>
       </c>
       <c r="H48" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E49" s="12">
-        <v>808300</v>
-      </c>
-      <c r="F49" s="12">
-        <v>10380100</v>
-      </c>
-      <c r="G49" s="12">
-        <v>-9571800</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>52</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B49" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" t="s">
+        <v>56</v>
+      </c>
+      <c r="D49" t="s">
+        <v>57</v>
+      </c>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8">
+        <v>159800</v>
+      </c>
+      <c r="G49" s="8">
+        <v>-1184400</v>
+      </c>
+      <c r="H49" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" t="s">
+        <v>58</v>
+      </c>
+      <c r="D50" t="s">
+        <v>59</v>
+      </c>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8">
+        <v>103400</v>
+      </c>
+      <c r="G50" s="8">
+        <v>-1287800</v>
+      </c>
+      <c r="H50" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
+      <c r="A51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51" t="s">
+        <v>60</v>
+      </c>
+      <c r="D51" t="s">
+        <v>61</v>
+      </c>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8">
+        <v>78960</v>
+      </c>
+      <c r="G51" s="8">
+        <v>-1366760</v>
+      </c>
+      <c r="H51" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H52" s="5" t="s">
-        <v>11</v>
+      <c r="A52" t="s">
+        <v>52</v>
+      </c>
+      <c r="B52" t="s">
+        <v>53</v>
+      </c>
+      <c r="C52" t="s">
+        <v>62</v>
+      </c>
+      <c r="D52" t="s">
+        <v>63</v>
+      </c>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8">
+        <v>90240</v>
+      </c>
+      <c r="G52" s="8">
+        <v>-1457000</v>
+      </c>
+      <c r="H52" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C53" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="D53" t="s">
-        <v>43</v>
-      </c>
-      <c r="E53" s="8">
-        <v>545750</v>
-      </c>
-      <c r="F53" s="8"/>
+        <v>65</v>
+      </c>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8">
+        <v>141000</v>
+      </c>
       <c r="G53" s="8">
-        <v>545750</v>
+        <v>-1598000</v>
       </c>
       <c r="H53" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C54" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E54" s="12">
-        <v>545750</v>
-      </c>
-      <c r="F54" s="12">
-        <v>0</v>
-      </c>
-      <c r="G54" s="12">
-        <v>545750</v>
-      </c>
-      <c r="H54" s="10" t="s">
-        <v>50</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>52</v>
+      </c>
+      <c r="B54" t="s">
+        <v>53</v>
+      </c>
+      <c r="C54" t="s">
+        <v>68</v>
+      </c>
+      <c r="D54" t="s">
+        <v>55</v>
+      </c>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8">
+        <v>225600</v>
+      </c>
+      <c r="G54" s="8">
+        <v>-1823600</v>
+      </c>
+      <c r="H54" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>52</v>
+      </c>
+      <c r="B55" t="s">
+        <v>53</v>
+      </c>
+      <c r="C55" t="s">
+        <v>69</v>
+      </c>
+      <c r="D55" t="s">
+        <v>57</v>
+      </c>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8">
+        <v>159800</v>
+      </c>
+      <c r="G55" s="8">
+        <v>-1983400</v>
+      </c>
+      <c r="H55" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
+      <c r="A56" t="s">
+        <v>52</v>
+      </c>
+      <c r="B56" t="s">
+        <v>53</v>
+      </c>
+      <c r="C56" t="s">
+        <v>70</v>
+      </c>
+      <c r="D56" t="s">
+        <v>59</v>
+      </c>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8">
+        <v>103400</v>
+      </c>
+      <c r="G56" s="8">
+        <v>-2086800</v>
+      </c>
+      <c r="H56" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H57" s="5" t="s">
-        <v>11</v>
+      <c r="A57" t="s">
+        <v>52</v>
+      </c>
+      <c r="B57" t="s">
+        <v>53</v>
+      </c>
+      <c r="C57" t="s">
+        <v>71</v>
+      </c>
+      <c r="D57" t="s">
+        <v>61</v>
+      </c>
+      <c r="E57" s="8"/>
+      <c r="F57" s="8">
+        <v>78960</v>
+      </c>
+      <c r="G57" s="8">
+        <v>-2165760</v>
+      </c>
+      <c r="H57" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="B58" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C58" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="D58" t="s">
-        <v>40</v>
-      </c>
-      <c r="E58" s="8">
-        <v>637200</v>
-      </c>
-      <c r="F58" s="8"/>
+        <v>63</v>
+      </c>
+      <c r="E58" s="8"/>
+      <c r="F58" s="8">
+        <v>90240</v>
+      </c>
       <c r="G58" s="8">
-        <v>637200</v>
+        <v>-2256000</v>
       </c>
       <c r="H58" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="B59" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C59" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="D59" t="s">
-        <v>48</v>
-      </c>
-      <c r="E59" s="8">
-        <v>925120</v>
-      </c>
-      <c r="F59" s="8"/>
+        <v>65</v>
+      </c>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8">
+        <v>141000</v>
+      </c>
       <c r="G59" s="8">
-        <v>1562320</v>
+        <v>-2397000</v>
       </c>
       <c r="H59" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D60" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E60" s="12">
-        <v>1562320</v>
-      </c>
-      <c r="F60" s="12">
-        <v>0</v>
-      </c>
-      <c r="G60" s="12">
-        <v>1562320</v>
-      </c>
-      <c r="H60" s="10" t="s">
-        <v>50</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>75</v>
+      </c>
+      <c r="B60" t="s">
+        <v>53</v>
+      </c>
+      <c r="C60" t="s">
+        <v>76</v>
+      </c>
+      <c r="D60" t="s">
+        <v>77</v>
+      </c>
+      <c r="E60" s="8">
+        <v>225600</v>
+      </c>
+      <c r="F60" s="8"/>
+      <c r="G60" s="8">
+        <v>-2171400</v>
+      </c>
+      <c r="H60" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>75</v>
+      </c>
+      <c r="B61" t="s">
+        <v>53</v>
+      </c>
+      <c r="C61" t="s">
+        <v>78</v>
+      </c>
+      <c r="D61" t="s">
+        <v>79</v>
+      </c>
+      <c r="E61" s="8">
+        <v>159800</v>
+      </c>
+      <c r="F61" s="8"/>
+      <c r="G61" s="8">
+        <v>-2011600</v>
+      </c>
+      <c r="H61" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
+      <c r="A62" t="s">
+        <v>75</v>
+      </c>
+      <c r="B62" t="s">
+        <v>53</v>
+      </c>
+      <c r="C62" t="s">
+        <v>80</v>
+      </c>
+      <c r="D62" t="s">
+        <v>81</v>
+      </c>
+      <c r="E62" s="8">
+        <v>103400</v>
+      </c>
+      <c r="F62" s="8"/>
+      <c r="G62" s="8">
+        <v>-1908200</v>
+      </c>
+      <c r="H62" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H63" s="5" t="s">
-        <v>11</v>
+      <c r="A63" t="s">
+        <v>75</v>
+      </c>
+      <c r="B63" t="s">
+        <v>53</v>
+      </c>
+      <c r="C63" t="s">
+        <v>82</v>
+      </c>
+      <c r="D63" t="s">
+        <v>83</v>
+      </c>
+      <c r="E63" s="8">
+        <v>78960</v>
+      </c>
+      <c r="F63" s="8"/>
+      <c r="G63" s="8">
+        <v>-1829240</v>
+      </c>
+      <c r="H63" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="B64" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C64" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="D64" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E64" s="8">
-        <v>620000</v>
+        <v>90240</v>
       </c>
       <c r="F64" s="8"/>
       <c r="G64" s="8">
-        <v>620000</v>
+        <v>-1739000</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C65" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D65" s="11" t="s">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>75</v>
+      </c>
+      <c r="B65" t="s">
+        <v>53</v>
+      </c>
+      <c r="C65" t="s">
+        <v>86</v>
+      </c>
+      <c r="D65" t="s">
+        <v>87</v>
+      </c>
+      <c r="E65" s="8">
+        <v>141000</v>
+      </c>
+      <c r="F65" s="8"/>
+      <c r="G65" s="8">
+        <v>-1598000</v>
+      </c>
+      <c r="H65" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E65" s="12">
-        <v>620000</v>
-      </c>
-      <c r="F65" s="12">
-        <v>0</v>
-      </c>
-      <c r="G65" s="12">
-        <v>620000</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4"/>
+      <c r="E66" s="12">
+        <v>799000</v>
+      </c>
+      <c r="F66" s="12">
+        <v>1598000</v>
+      </c>
+      <c r="G66" s="12">
+        <v>-1598000</v>
+      </c>
+      <c r="H66" s="10" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="5" t="s">
+      <c r="A68" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B69" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C68" s="5" t="s">
+      <c r="C69" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D68" s="5" t="s">
+      <c r="D69" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E68" s="5" t="s">
+      <c r="E69" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F68" s="5" t="s">
+      <c r="F69" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G68" s="5" t="s">
+      <c r="G69" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H68" s="5" t="s">
+      <c r="H69" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+    <row r="70" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="7">
+        <v>-225780</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>52</v>
+      </c>
+      <c r="B71" t="s">
+        <v>53</v>
+      </c>
+      <c r="C71" t="s">
         <v>54</v>
       </c>
-      <c r="B69" t="s">
+      <c r="D71" t="s">
         <v>55</v>
       </c>
-      <c r="C69" t="s">
+      <c r="E71" s="8"/>
+      <c r="F71" s="8">
+        <v>88410</v>
+      </c>
+      <c r="G71" s="8">
+        <v>-314190</v>
+      </c>
+      <c r="H71" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>52</v>
+      </c>
+      <c r="B72" t="s">
+        <v>53</v>
+      </c>
+      <c r="C72" t="s">
         <v>56</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D72" t="s">
         <v>57</v>
       </c>
-      <c r="E69" s="8">
-        <v>740000</v>
-      </c>
-      <c r="F69" s="8"/>
-      <c r="G69" s="8">
-        <v>740000</v>
-      </c>
-      <c r="H69" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>64</v>
-      </c>
-      <c r="B70" t="s">
-        <v>55</v>
-      </c>
-      <c r="C70" t="s">
-        <v>65</v>
-      </c>
-      <c r="D70" t="s">
-        <v>66</v>
-      </c>
-      <c r="E70" s="8">
-        <v>950000</v>
-      </c>
-      <c r="F70" s="8"/>
-      <c r="G70" s="8">
-        <v>1690000</v>
-      </c>
-      <c r="H70" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C71" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D71" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E71" s="12">
-        <v>1690000</v>
-      </c>
-      <c r="F71" s="12">
-        <v>0</v>
-      </c>
-      <c r="G71" s="12">
-        <v>1690000</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>50</v>
+      <c r="E72" s="8"/>
+      <c r="F72" s="8">
+        <v>49395</v>
+      </c>
+      <c r="G72" s="8">
+        <v>-363585</v>
+      </c>
+      <c r="H72" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
+      <c r="A73" t="s">
+        <v>52</v>
+      </c>
+      <c r="B73" t="s">
+        <v>53</v>
+      </c>
+      <c r="C73" t="s">
+        <v>58</v>
+      </c>
+      <c r="D73" t="s">
+        <v>59</v>
+      </c>
+      <c r="E73" s="8"/>
+      <c r="F73" s="8">
+        <v>21285</v>
+      </c>
+      <c r="G73" s="8">
+        <v>-384870</v>
+      </c>
+      <c r="H73" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G74" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H74" s="5" t="s">
-        <v>11</v>
+      <c r="A74" t="s">
+        <v>52</v>
+      </c>
+      <c r="B74" t="s">
+        <v>53</v>
+      </c>
+      <c r="C74" t="s">
+        <v>60</v>
+      </c>
+      <c r="D74" t="s">
+        <v>61</v>
+      </c>
+      <c r="E74" s="8"/>
+      <c r="F74" s="8">
+        <v>11927</v>
+      </c>
+      <c r="G74" s="8">
+        <v>-396797</v>
+      </c>
+      <c r="H74" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="B75" t="s">
+        <v>53</v>
+      </c>
+      <c r="C75" t="s">
+        <v>62</v>
+      </c>
+      <c r="D75" t="s">
+        <v>63</v>
+      </c>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8">
+        <v>14738</v>
+      </c>
+      <c r="G75" s="8">
+        <v>-411535</v>
+      </c>
+      <c r="H75" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>52</v>
+      </c>
+      <c r="B76" t="s">
+        <v>53</v>
+      </c>
+      <c r="C76" t="s">
+        <v>64</v>
+      </c>
+      <c r="D76" t="s">
+        <v>65</v>
+      </c>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8">
+        <v>40025</v>
+      </c>
+      <c r="G76" s="8">
+        <v>-451560</v>
+      </c>
+      <c r="H76" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>52</v>
+      </c>
+      <c r="B77" t="s">
+        <v>53</v>
+      </c>
+      <c r="C77" t="s">
+        <v>68</v>
+      </c>
+      <c r="D77" t="s">
         <v>55</v>
       </c>
-      <c r="C75" t="s">
-        <v>68</v>
-      </c>
-      <c r="D75" t="s">
+      <c r="E77" s="8"/>
+      <c r="F77" s="8">
+        <v>88410</v>
+      </c>
+      <c r="G77" s="8">
+        <v>-539970</v>
+      </c>
+      <c r="H77" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>52</v>
+      </c>
+      <c r="B78" t="s">
+        <v>53</v>
+      </c>
+      <c r="C78" t="s">
         <v>69</v>
       </c>
-      <c r="E75" s="8">
-        <v>2500000</v>
-      </c>
-      <c r="F75" s="8"/>
-      <c r="G75" s="8">
-        <v>2500000</v>
-      </c>
-      <c r="H75" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C76" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D76" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E76" s="12">
-        <v>2500000</v>
-      </c>
-      <c r="F76" s="12">
-        <v>0</v>
-      </c>
-      <c r="G76" s="12">
-        <v>2500000</v>
-      </c>
-      <c r="H76" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
+      <c r="D78" t="s">
+        <v>57</v>
+      </c>
+      <c r="E78" s="8"/>
+      <c r="F78" s="8">
+        <v>49395</v>
+      </c>
+      <c r="G78" s="8">
+        <v>-589365</v>
+      </c>
+      <c r="H78" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G79" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H79" s="5" t="s">
-        <v>11</v>
+      <c r="A79" t="s">
+        <v>52</v>
+      </c>
+      <c r="B79" t="s">
+        <v>53</v>
+      </c>
+      <c r="C79" t="s">
+        <v>70</v>
+      </c>
+      <c r="D79" t="s">
+        <v>59</v>
+      </c>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8">
+        <v>21285</v>
+      </c>
+      <c r="G79" s="8">
+        <v>-610650</v>
+      </c>
+      <c r="H79" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>52</v>
+      </c>
+      <c r="B80" t="s">
+        <v>53</v>
+      </c>
+      <c r="C80" t="s">
+        <v>71</v>
+      </c>
+      <c r="D80" t="s">
         <v>61</v>
       </c>
-      <c r="B80" t="s">
-        <v>55</v>
-      </c>
-      <c r="C80" t="s">
-        <v>62</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="E80" s="8"/>
+      <c r="F80" s="8">
+        <v>11927</v>
+      </c>
+      <c r="G80" s="8">
+        <v>-622577</v>
+      </c>
+      <c r="H80" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>52</v>
+      </c>
+      <c r="B81" t="s">
+        <v>53</v>
+      </c>
+      <c r="C81" t="s">
+        <v>72</v>
+      </c>
+      <c r="D81" t="s">
         <v>63</v>
       </c>
-      <c r="E80" s="8">
-        <v>385000</v>
-      </c>
-      <c r="F80" s="8"/>
-      <c r="G80" s="8">
-        <v>385000</v>
-      </c>
-      <c r="H80" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C81" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D81" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E81" s="12">
-        <v>385000</v>
-      </c>
-      <c r="F81" s="12">
-        <v>0</v>
-      </c>
-      <c r="G81" s="12">
-        <v>385000</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>50</v>
+      <c r="E81" s="8"/>
+      <c r="F81" s="8">
+        <v>14738</v>
+      </c>
+      <c r="G81" s="8">
+        <v>-637315</v>
+      </c>
+      <c r="H81" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>52</v>
+      </c>
+      <c r="B82" t="s">
+        <v>53</v>
+      </c>
+      <c r="C82" t="s">
+        <v>73</v>
+      </c>
+      <c r="D82" t="s">
+        <v>65</v>
+      </c>
+      <c r="E82" s="8"/>
+      <c r="F82" s="8">
+        <v>40025</v>
+      </c>
+      <c r="G82" s="8">
+        <v>-677340</v>
+      </c>
+      <c r="H82" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
-      <c r="F83" s="4"/>
-      <c r="G83" s="4"/>
-      <c r="H83" s="4"/>
+      <c r="A83" t="s">
+        <v>75</v>
+      </c>
+      <c r="B83" t="s">
+        <v>53</v>
+      </c>
+      <c r="C83" t="s">
+        <v>76</v>
+      </c>
+      <c r="D83" t="s">
+        <v>77</v>
+      </c>
+      <c r="E83" s="8">
+        <v>88410</v>
+      </c>
+      <c r="F83" s="8"/>
+      <c r="G83" s="8">
+        <v>-588930</v>
+      </c>
+      <c r="H83" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G84" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H84" s="5" t="s">
-        <v>11</v>
+      <c r="A84" t="s">
+        <v>75</v>
+      </c>
+      <c r="B84" t="s">
+        <v>53</v>
+      </c>
+      <c r="C84" t="s">
+        <v>78</v>
+      </c>
+      <c r="D84" t="s">
+        <v>79</v>
+      </c>
+      <c r="E84" s="8">
+        <v>49395</v>
+      </c>
+      <c r="F84" s="8"/>
+      <c r="G84" s="8">
+        <v>-539535</v>
+      </c>
+      <c r="H84" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B85" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="C85" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D85" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E85" s="8">
-        <v>4250000</v>
+        <v>21285</v>
       </c>
       <c r="F85" s="8"/>
       <c r="G85" s="8">
-        <v>4250000</v>
+        <v>-518250</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C86" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D86" s="11" t="s">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>75</v>
+      </c>
+      <c r="B86" t="s">
+        <v>53</v>
+      </c>
+      <c r="C86" t="s">
+        <v>82</v>
+      </c>
+      <c r="D86" t="s">
+        <v>83</v>
+      </c>
+      <c r="E86" s="8">
+        <v>11927</v>
+      </c>
+      <c r="F86" s="8"/>
+      <c r="G86" s="8">
+        <v>-506323</v>
+      </c>
+      <c r="H86" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>75</v>
+      </c>
+      <c r="B87" t="s">
+        <v>53</v>
+      </c>
+      <c r="C87" t="s">
+        <v>84</v>
+      </c>
+      <c r="D87" t="s">
+        <v>85</v>
+      </c>
+      <c r="E87" s="8">
+        <v>14738</v>
+      </c>
+      <c r="F87" s="8"/>
+      <c r="G87" s="8">
+        <v>-491585</v>
+      </c>
+      <c r="H87" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>75</v>
+      </c>
+      <c r="B88" t="s">
+        <v>53</v>
+      </c>
+      <c r="C88" t="s">
+        <v>86</v>
+      </c>
+      <c r="D88" t="s">
+        <v>87</v>
+      </c>
+      <c r="E88" s="8">
+        <v>40025</v>
+      </c>
+      <c r="F88" s="8"/>
+      <c r="G88" s="8">
+        <v>-451560</v>
+      </c>
+      <c r="H88" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C89" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D89" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E86" s="12">
-        <v>4250000</v>
-      </c>
-      <c r="F86" s="12">
-        <v>0</v>
-      </c>
-      <c r="G86" s="12">
-        <v>4250000</v>
-      </c>
-      <c r="H86" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="4"/>
-      <c r="H88" s="4"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="5" t="s">
+      <c r="E89" s="12">
+        <v>225780</v>
+      </c>
+      <c r="F89" s="12">
+        <v>451560</v>
+      </c>
+      <c r="G89" s="12">
+        <v>-451560</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B91" s="4"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B89" s="5" t="s">
+      <c r="B92" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C89" s="5" t="s">
+      <c r="C92" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D89" s="5" t="s">
+      <c r="D92" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E89" s="5" t="s">
+      <c r="E92" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F89" s="5" t="s">
+      <c r="F92" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G89" s="5" t="s">
+      <c r="G92" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H89" s="5" t="s">
+      <c r="H92" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="6" t="s">
+    <row r="93" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B90" s="6" t="s">
+      <c r="B93" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C90" s="6" t="s">
+      <c r="C93" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D90" s="6" t="s">
+      <c r="D93" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E90" s="7"/>
-      <c r="F90" s="7"/>
-      <c r="G90" s="7">
-        <v>-3140000</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+      <c r="E93" s="7"/>
+      <c r="F93" s="7"/>
+      <c r="G93" s="7">
+        <v>-565200</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>16</v>
+      </c>
+      <c r="B94" t="s">
+        <v>17</v>
+      </c>
+      <c r="C94" t="s">
+        <v>18</v>
+      </c>
+      <c r="D94" t="s">
+        <v>19</v>
+      </c>
+      <c r="E94" s="8"/>
+      <c r="F94" s="8">
+        <v>162000</v>
+      </c>
+      <c r="G94" s="8">
+        <v>-727200</v>
+      </c>
+      <c r="H94" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>20</v>
+      </c>
+      <c r="B95" t="s">
+        <v>17</v>
+      </c>
+      <c r="C95" t="s">
+        <v>21</v>
+      </c>
+      <c r="D95" t="s">
+        <v>22</v>
+      </c>
+      <c r="E95" s="8"/>
+      <c r="F95" s="8">
+        <v>67500</v>
+      </c>
+      <c r="G95" s="8">
+        <v>-794700</v>
+      </c>
+      <c r="H95" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>24</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B96" t="s">
         <v>17</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C96" t="s">
         <v>25</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D96" t="s">
         <v>26</v>
       </c>
-      <c r="E91" s="8"/>
-      <c r="F91" s="8">
-        <v>490000</v>
-      </c>
-      <c r="G91" s="8">
-        <v>-3630000</v>
-      </c>
-      <c r="H91" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>30</v>
-      </c>
-      <c r="B92" t="s">
-        <v>17</v>
-      </c>
-      <c r="C92" t="s">
-        <v>31</v>
-      </c>
-      <c r="D92" t="s">
-        <v>32</v>
-      </c>
-      <c r="E92" s="8"/>
-      <c r="F92" s="8">
-        <v>784000</v>
-      </c>
-      <c r="G92" s="8">
-        <v>-4414000</v>
-      </c>
-      <c r="H92" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C93" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D93" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E93" s="12">
-        <v>0</v>
-      </c>
-      <c r="F93" s="12">
-        <v>1274000</v>
-      </c>
-      <c r="G93" s="12">
-        <v>-4414000</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B96" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F96" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G96" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H96" s="5" t="s">
-        <v>11</v>
+      <c r="E96" s="8"/>
+      <c r="F96" s="8">
+        <v>88200</v>
+      </c>
+      <c r="G96" s="8">
+        <v>-882900</v>
+      </c>
+      <c r="H96" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B97" t="s">
         <v>17</v>
       </c>
       <c r="C97" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D97" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E97" s="8"/>
       <c r="F97" s="8">
-        <v>900000</v>
+        <v>131400</v>
       </c>
       <c r="G97" s="8">
-        <v>-900000</v>
+        <v>-1014300</v>
       </c>
       <c r="H97" t="s">
         <v>15</v>
@@ -2601,101 +2990,2825 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B98" t="s">
         <v>17</v>
       </c>
       <c r="C98" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D98" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E98" s="8"/>
       <c r="F98" s="8">
+        <v>141120</v>
+      </c>
+      <c r="G98" s="8">
+        <v>-1155420</v>
+      </c>
+      <c r="H98" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C99" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D99" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E99" s="12">
+        <v>0</v>
+      </c>
+      <c r="F99" s="12">
+        <v>590220</v>
+      </c>
+      <c r="G99" s="12">
+        <v>-1155420</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B101" s="4"/>
+      <c r="C101" s="4"/>
+      <c r="D101" s="4"/>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+      <c r="G101" s="4"/>
+      <c r="H101" s="4"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E102" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F102" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G102" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H102" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>95</v>
+      </c>
+      <c r="B103" t="s">
+        <v>96</v>
+      </c>
+      <c r="C103" t="s">
+        <v>97</v>
+      </c>
+      <c r="D103" t="s">
+        <v>98</v>
+      </c>
+      <c r="E103" s="8">
+        <v>133200</v>
+      </c>
+      <c r="F103" s="8"/>
+      <c r="G103" s="8">
+        <v>133200</v>
+      </c>
+      <c r="H103" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>99</v>
+      </c>
+      <c r="B104" t="s">
+        <v>96</v>
+      </c>
+      <c r="C104" t="s">
+        <v>100</v>
+      </c>
+      <c r="D104" t="s">
+        <v>101</v>
+      </c>
+      <c r="E104" s="8">
+        <v>111600</v>
+      </c>
+      <c r="F104" s="8"/>
+      <c r="G104" s="8">
+        <v>244800</v>
+      </c>
+      <c r="H104" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>102</v>
+      </c>
+      <c r="B105" t="s">
+        <v>96</v>
+      </c>
+      <c r="C105" t="s">
+        <v>103</v>
+      </c>
+      <c r="D105" t="s">
+        <v>104</v>
+      </c>
+      <c r="E105" s="8">
+        <v>69300</v>
+      </c>
+      <c r="F105" s="8"/>
+      <c r="G105" s="8">
+        <v>314100</v>
+      </c>
+      <c r="H105" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>96</v>
+      </c>
+      <c r="C106" t="s">
+        <v>106</v>
+      </c>
+      <c r="D106" t="s">
+        <v>107</v>
+      </c>
+      <c r="E106" s="8">
+        <v>171000</v>
+      </c>
+      <c r="F106" s="8"/>
+      <c r="G106" s="8">
+        <v>485100</v>
+      </c>
+      <c r="H106" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>108</v>
+      </c>
+      <c r="B107" t="s">
+        <v>96</v>
+      </c>
+      <c r="C107" t="s">
+        <v>109</v>
+      </c>
+      <c r="D107" t="s">
+        <v>110</v>
+      </c>
+      <c r="E107" s="8">
+        <v>450000</v>
+      </c>
+      <c r="F107" s="8"/>
+      <c r="G107" s="8">
+        <v>935100</v>
+      </c>
+      <c r="H107" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D108" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E108" s="12">
+        <v>935100</v>
+      </c>
+      <c r="F108" s="12">
+        <v>0</v>
+      </c>
+      <c r="G108" s="12">
+        <v>935100</v>
+      </c>
+      <c r="H108" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B110" s="4"/>
+      <c r="C110" s="4"/>
+      <c r="D110" s="4"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
+      <c r="G110" s="4"/>
+      <c r="H110" s="4"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E111" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F111" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G111" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H111" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>95</v>
+      </c>
+      <c r="B112" t="s">
+        <v>96</v>
+      </c>
+      <c r="C112" t="s">
+        <v>97</v>
+      </c>
+      <c r="D112" t="s">
+        <v>98</v>
+      </c>
+      <c r="E112" s="8"/>
+      <c r="F112" s="8">
+        <v>873200</v>
+      </c>
+      <c r="G112" s="8">
+        <v>-873200</v>
+      </c>
+      <c r="H112" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>99</v>
+      </c>
+      <c r="B113" t="s">
+        <v>96</v>
+      </c>
+      <c r="C113" t="s">
+        <v>100</v>
+      </c>
+      <c r="D113" t="s">
+        <v>101</v>
+      </c>
+      <c r="E113" s="8"/>
+      <c r="F113" s="8">
+        <v>731600</v>
+      </c>
+      <c r="G113" s="8">
+        <v>-1604800</v>
+      </c>
+      <c r="H113" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>102</v>
+      </c>
+      <c r="B114" t="s">
+        <v>96</v>
+      </c>
+      <c r="C114" t="s">
+        <v>103</v>
+      </c>
+      <c r="D114" t="s">
+        <v>104</v>
+      </c>
+      <c r="E114" s="8"/>
+      <c r="F114" s="8">
+        <v>454300</v>
+      </c>
+      <c r="G114" s="8">
+        <v>-2059100</v>
+      </c>
+      <c r="H114" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>105</v>
+      </c>
+      <c r="B115" t="s">
+        <v>96</v>
+      </c>
+      <c r="C115" t="s">
+        <v>106</v>
+      </c>
+      <c r="D115" t="s">
+        <v>107</v>
+      </c>
+      <c r="E115" s="8"/>
+      <c r="F115" s="8">
+        <v>1121000</v>
+      </c>
+      <c r="G115" s="8">
+        <v>-3180100</v>
+      </c>
+      <c r="H115" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>112</v>
+      </c>
+      <c r="B116" t="s">
+        <v>53</v>
+      </c>
+      <c r="C116" t="s">
+        <v>113</v>
+      </c>
+      <c r="D116" t="s">
+        <v>114</v>
+      </c>
+      <c r="E116" s="8"/>
+      <c r="F116" s="8">
+        <v>4250000</v>
+      </c>
+      <c r="G116" s="8">
+        <v>-7430100</v>
+      </c>
+      <c r="H116" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>108</v>
+      </c>
+      <c r="B117" t="s">
+        <v>96</v>
+      </c>
+      <c r="C117" t="s">
+        <v>109</v>
+      </c>
+      <c r="D117" t="s">
+        <v>110</v>
+      </c>
+      <c r="E117" s="8"/>
+      <c r="F117" s="8">
+        <v>2950000</v>
+      </c>
+      <c r="G117" s="8">
+        <v>-10380100</v>
+      </c>
+      <c r="H117" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>34</v>
+      </c>
+      <c r="B118" t="s">
+        <v>35</v>
+      </c>
+      <c r="C118" t="s">
+        <v>36</v>
+      </c>
+      <c r="D118" t="s">
+        <v>37</v>
+      </c>
+      <c r="E118" s="8">
+        <v>365800</v>
+      </c>
+      <c r="F118" s="8"/>
+      <c r="G118" s="8">
+        <v>-10014300</v>
+      </c>
+      <c r="H118" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>34</v>
+      </c>
+      <c r="B119" t="s">
+        <v>35</v>
+      </c>
+      <c r="C119" t="s">
+        <v>45</v>
+      </c>
+      <c r="D119" t="s">
+        <v>46</v>
+      </c>
+      <c r="E119" s="8">
+        <v>442500</v>
+      </c>
+      <c r="F119" s="8"/>
+      <c r="G119" s="8">
+        <v>-9571800</v>
+      </c>
+      <c r="H119" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C120" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D120" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E120" s="12">
+        <v>808300</v>
+      </c>
+      <c r="F120" s="12">
+        <v>10380100</v>
+      </c>
+      <c r="G120" s="12">
+        <v>-9571800</v>
+      </c>
+      <c r="H120" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B122" s="4"/>
+      <c r="C122" s="4"/>
+      <c r="D122" s="4"/>
+      <c r="E122" s="4"/>
+      <c r="F122" s="4"/>
+      <c r="G122" s="4"/>
+      <c r="H122" s="4"/>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D123" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E123" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F123" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G123" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H123" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E124" s="7"/>
+      <c r="F124" s="7"/>
+      <c r="G124" s="7">
+        <v>-3756470</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>52</v>
+      </c>
+      <c r="B125" t="s">
+        <v>53</v>
+      </c>
+      <c r="C125" t="s">
+        <v>66</v>
+      </c>
+      <c r="D125" t="s">
+        <v>67</v>
+      </c>
+      <c r="E125" s="8"/>
+      <c r="F125" s="8">
+        <v>3756470</v>
+      </c>
+      <c r="G125" s="8">
+        <v>-7512940</v>
+      </c>
+      <c r="H125" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>52</v>
+      </c>
+      <c r="B126" t="s">
+        <v>53</v>
+      </c>
+      <c r="C126" t="s">
+        <v>74</v>
+      </c>
+      <c r="D126" t="s">
+        <v>67</v>
+      </c>
+      <c r="E126" s="8"/>
+      <c r="F126" s="8">
+        <v>3756470</v>
+      </c>
+      <c r="G126" s="8">
+        <v>-11269410</v>
+      </c>
+      <c r="H126" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>75</v>
+      </c>
+      <c r="B127" t="s">
+        <v>53</v>
+      </c>
+      <c r="C127" t="s">
+        <v>88</v>
+      </c>
+      <c r="D127" t="s">
+        <v>89</v>
+      </c>
+      <c r="E127" s="8">
+        <v>3756470</v>
+      </c>
+      <c r="F127" s="8"/>
+      <c r="G127" s="8">
+        <v>-7512940</v>
+      </c>
+      <c r="H127" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C128" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D128" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E128" s="12">
+        <v>3756470</v>
+      </c>
+      <c r="F128" s="12">
+        <v>7512940</v>
+      </c>
+      <c r="G128" s="12">
+        <v>-7512940</v>
+      </c>
+      <c r="H128" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B130" s="4"/>
+      <c r="C130" s="4"/>
+      <c r="D130" s="4"/>
+      <c r="E130" s="4"/>
+      <c r="F130" s="4"/>
+      <c r="G130" s="4"/>
+      <c r="H130" s="4"/>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E131" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F131" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G131" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H131" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>34</v>
+      </c>
+      <c r="B132" t="s">
+        <v>35</v>
+      </c>
+      <c r="C132" t="s">
+        <v>42</v>
+      </c>
+      <c r="D132" t="s">
+        <v>43</v>
+      </c>
+      <c r="E132" s="8">
+        <v>545750</v>
+      </c>
+      <c r="F132" s="8"/>
+      <c r="G132" s="8">
+        <v>545750</v>
+      </c>
+      <c r="H132" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C133" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D133" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E133" s="12">
+        <v>545750</v>
+      </c>
+      <c r="F133" s="12">
+        <v>0</v>
+      </c>
+      <c r="G133" s="12">
+        <v>545750</v>
+      </c>
+      <c r="H133" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B135" s="4"/>
+      <c r="C135" s="4"/>
+      <c r="D135" s="4"/>
+      <c r="E135" s="4"/>
+      <c r="F135" s="4"/>
+      <c r="G135" s="4"/>
+      <c r="H135" s="4"/>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E136" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F136" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G136" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H136" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>34</v>
+      </c>
+      <c r="B137" t="s">
+        <v>35</v>
+      </c>
+      <c r="C137" t="s">
+        <v>39</v>
+      </c>
+      <c r="D137" t="s">
+        <v>40</v>
+      </c>
+      <c r="E137" s="8">
+        <v>637200</v>
+      </c>
+      <c r="F137" s="8"/>
+      <c r="G137" s="8">
+        <v>637200</v>
+      </c>
+      <c r="H137" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>34</v>
+      </c>
+      <c r="B138" t="s">
+        <v>35</v>
+      </c>
+      <c r="C138" t="s">
+        <v>47</v>
+      </c>
+      <c r="D138" t="s">
+        <v>48</v>
+      </c>
+      <c r="E138" s="8">
+        <v>925120</v>
+      </c>
+      <c r="F138" s="8"/>
+      <c r="G138" s="8">
+        <v>1562320</v>
+      </c>
+      <c r="H138" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C139" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D139" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E139" s="12">
+        <v>1562320</v>
+      </c>
+      <c r="F139" s="12">
+        <v>0</v>
+      </c>
+      <c r="G139" s="12">
+        <v>1562320</v>
+      </c>
+      <c r="H139" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B141" s="4"/>
+      <c r="C141" s="4"/>
+      <c r="D141" s="4"/>
+      <c r="E141" s="4"/>
+      <c r="F141" s="4"/>
+      <c r="G141" s="4"/>
+      <c r="H141" s="4"/>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F142" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H142" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>99</v>
+      </c>
+      <c r="B143" t="s">
+        <v>96</v>
+      </c>
+      <c r="C143" t="s">
+        <v>100</v>
+      </c>
+      <c r="D143" t="s">
+        <v>101</v>
+      </c>
+      <c r="E143" s="8">
+        <v>620000</v>
+      </c>
+      <c r="F143" s="8"/>
+      <c r="G143" s="8">
+        <v>620000</v>
+      </c>
+      <c r="H143" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C144" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D144" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E144" s="12">
+        <v>620000</v>
+      </c>
+      <c r="F144" s="12">
+        <v>0</v>
+      </c>
+      <c r="G144" s="12">
+        <v>620000</v>
+      </c>
+      <c r="H144" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B146" s="4"/>
+      <c r="C146" s="4"/>
+      <c r="D146" s="4"/>
+      <c r="E146" s="4"/>
+      <c r="F146" s="4"/>
+      <c r="G146" s="4"/>
+      <c r="H146" s="4"/>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D147" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E147" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F147" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G147" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H147" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>95</v>
+      </c>
+      <c r="B148" t="s">
+        <v>96</v>
+      </c>
+      <c r="C148" t="s">
+        <v>97</v>
+      </c>
+      <c r="D148" t="s">
+        <v>98</v>
+      </c>
+      <c r="E148" s="8">
+        <v>740000</v>
+      </c>
+      <c r="F148" s="8"/>
+      <c r="G148" s="8">
+        <v>740000</v>
+      </c>
+      <c r="H148" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>105</v>
+      </c>
+      <c r="B149" t="s">
+        <v>96</v>
+      </c>
+      <c r="C149" t="s">
+        <v>106</v>
+      </c>
+      <c r="D149" t="s">
+        <v>107</v>
+      </c>
+      <c r="E149" s="8">
+        <v>950000</v>
+      </c>
+      <c r="F149" s="8"/>
+      <c r="G149" s="8">
+        <v>1690000</v>
+      </c>
+      <c r="H149" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C150" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D150" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E150" s="12">
+        <v>1690000</v>
+      </c>
+      <c r="F150" s="12">
+        <v>0</v>
+      </c>
+      <c r="G150" s="12">
+        <v>1690000</v>
+      </c>
+      <c r="H150" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B152" s="4"/>
+      <c r="C152" s="4"/>
+      <c r="D152" s="4"/>
+      <c r="E152" s="4"/>
+      <c r="F152" s="4"/>
+      <c r="G152" s="4"/>
+      <c r="H152" s="4"/>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E153" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F153" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G153" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H153" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>108</v>
+      </c>
+      <c r="B154" t="s">
+        <v>96</v>
+      </c>
+      <c r="C154" t="s">
+        <v>109</v>
+      </c>
+      <c r="D154" t="s">
+        <v>110</v>
+      </c>
+      <c r="E154" s="8">
+        <v>2500000</v>
+      </c>
+      <c r="F154" s="8"/>
+      <c r="G154" s="8">
+        <v>2500000</v>
+      </c>
+      <c r="H154" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C155" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D155" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E155" s="12">
+        <v>2500000</v>
+      </c>
+      <c r="F155" s="12">
+        <v>0</v>
+      </c>
+      <c r="G155" s="12">
+        <v>2500000</v>
+      </c>
+      <c r="H155" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B157" s="4"/>
+      <c r="C157" s="4"/>
+      <c r="D157" s="4"/>
+      <c r="E157" s="4"/>
+      <c r="F157" s="4"/>
+      <c r="G157" s="4"/>
+      <c r="H157" s="4"/>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D158" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E158" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G158" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H158" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>102</v>
+      </c>
+      <c r="B159" t="s">
+        <v>96</v>
+      </c>
+      <c r="C159" t="s">
+        <v>103</v>
+      </c>
+      <c r="D159" t="s">
+        <v>104</v>
+      </c>
+      <c r="E159" s="8">
+        <v>385000</v>
+      </c>
+      <c r="F159" s="8"/>
+      <c r="G159" s="8">
+        <v>385000</v>
+      </c>
+      <c r="H159" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C160" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D160" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E160" s="12">
+        <v>385000</v>
+      </c>
+      <c r="F160" s="12">
+        <v>0</v>
+      </c>
+      <c r="G160" s="12">
+        <v>385000</v>
+      </c>
+      <c r="H160" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B162" s="4"/>
+      <c r="C162" s="4"/>
+      <c r="D162" s="4"/>
+      <c r="E162" s="4"/>
+      <c r="F162" s="4"/>
+      <c r="G162" s="4"/>
+      <c r="H162" s="4"/>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D163" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E163" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F163" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G163" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H163" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>112</v>
+      </c>
+      <c r="B164" t="s">
+        <v>53</v>
+      </c>
+      <c r="C164" t="s">
+        <v>113</v>
+      </c>
+      <c r="D164" t="s">
+        <v>114</v>
+      </c>
+      <c r="E164" s="8">
+        <v>4250000</v>
+      </c>
+      <c r="F164" s="8"/>
+      <c r="G164" s="8">
+        <v>4250000</v>
+      </c>
+      <c r="H164" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C165" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D165" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E165" s="12">
+        <v>4250000</v>
+      </c>
+      <c r="F165" s="12">
+        <v>0</v>
+      </c>
+      <c r="G165" s="12">
+        <v>4250000</v>
+      </c>
+      <c r="H165" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B167" s="4"/>
+      <c r="C167" s="4"/>
+      <c r="D167" s="4"/>
+      <c r="E167" s="4"/>
+      <c r="F167" s="4"/>
+      <c r="G167" s="4"/>
+      <c r="H167" s="4"/>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D168" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E168" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G168" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H168" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D169" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E169" s="7"/>
+      <c r="F169" s="7"/>
+      <c r="G169" s="7">
+        <v>420000</v>
+      </c>
+      <c r="H169" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>52</v>
+      </c>
+      <c r="B170" t="s">
+        <v>53</v>
+      </c>
+      <c r="C170" t="s">
+        <v>60</v>
+      </c>
+      <c r="D170" t="s">
+        <v>61</v>
+      </c>
+      <c r="E170" s="8">
+        <v>420000</v>
+      </c>
+      <c r="F170" s="8"/>
+      <c r="G170" s="8">
+        <v>840000</v>
+      </c>
+      <c r="H170" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>52</v>
+      </c>
+      <c r="B171" t="s">
+        <v>53</v>
+      </c>
+      <c r="C171" t="s">
+        <v>71</v>
+      </c>
+      <c r="D171" t="s">
+        <v>61</v>
+      </c>
+      <c r="E171" s="8">
+        <v>420000</v>
+      </c>
+      <c r="F171" s="8"/>
+      <c r="G171" s="8">
+        <v>1260000</v>
+      </c>
+      <c r="H171" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>75</v>
+      </c>
+      <c r="B172" t="s">
+        <v>53</v>
+      </c>
+      <c r="C172" t="s">
+        <v>82</v>
+      </c>
+      <c r="D172" t="s">
+        <v>83</v>
+      </c>
+      <c r="E172" s="8"/>
+      <c r="F172" s="8">
+        <v>420000</v>
+      </c>
+      <c r="G172" s="8">
+        <v>840000</v>
+      </c>
+      <c r="H172" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C173" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D173" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E173" s="12">
+        <v>840000</v>
+      </c>
+      <c r="F173" s="12">
+        <v>420000</v>
+      </c>
+      <c r="G173" s="12">
+        <v>840000</v>
+      </c>
+      <c r="H173" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B175" s="4"/>
+      <c r="C175" s="4"/>
+      <c r="D175" s="4"/>
+      <c r="E175" s="4"/>
+      <c r="F175" s="4"/>
+      <c r="G175" s="4"/>
+      <c r="H175" s="4"/>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D176" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E176" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G176" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H176" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D177" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E177" s="7"/>
+      <c r="F177" s="7"/>
+      <c r="G177" s="7">
+        <v>2630000</v>
+      </c>
+      <c r="H177" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>52</v>
+      </c>
+      <c r="B178" t="s">
+        <v>53</v>
+      </c>
+      <c r="C178" t="s">
+        <v>56</v>
+      </c>
+      <c r="D178" t="s">
+        <v>57</v>
+      </c>
+      <c r="E178" s="8">
+        <v>850000</v>
+      </c>
+      <c r="F178" s="8"/>
+      <c r="G178" s="8">
+        <v>3480000</v>
+      </c>
+      <c r="H178" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>52</v>
+      </c>
+      <c r="B179" t="s">
+        <v>53</v>
+      </c>
+      <c r="C179" t="s">
+        <v>58</v>
+      </c>
+      <c r="D179" t="s">
+        <v>59</v>
+      </c>
+      <c r="E179" s="8">
+        <v>550000</v>
+      </c>
+      <c r="F179" s="8"/>
+      <c r="G179" s="8">
+        <v>4030000</v>
+      </c>
+      <c r="H179" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>52</v>
+      </c>
+      <c r="B180" t="s">
+        <v>53</v>
+      </c>
+      <c r="C180" t="s">
+        <v>62</v>
+      </c>
+      <c r="D180" t="s">
+        <v>63</v>
+      </c>
+      <c r="E180" s="8">
+        <v>480000</v>
+      </c>
+      <c r="F180" s="8"/>
+      <c r="G180" s="8">
+        <v>4510000</v>
+      </c>
+      <c r="H180" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>52</v>
+      </c>
+      <c r="B181" t="s">
+        <v>53</v>
+      </c>
+      <c r="C181" t="s">
+        <v>64</v>
+      </c>
+      <c r="D181" t="s">
+        <v>65</v>
+      </c>
+      <c r="E181" s="8">
+        <v>750000</v>
+      </c>
+      <c r="F181" s="8"/>
+      <c r="G181" s="8">
+        <v>5260000</v>
+      </c>
+      <c r="H181" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>52</v>
+      </c>
+      <c r="B182" t="s">
+        <v>53</v>
+      </c>
+      <c r="C182" t="s">
+        <v>69</v>
+      </c>
+      <c r="D182" t="s">
+        <v>57</v>
+      </c>
+      <c r="E182" s="8">
+        <v>850000</v>
+      </c>
+      <c r="F182" s="8"/>
+      <c r="G182" s="8">
+        <v>6110000</v>
+      </c>
+      <c r="H182" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>52</v>
+      </c>
+      <c r="B183" t="s">
+        <v>53</v>
+      </c>
+      <c r="C183" t="s">
+        <v>70</v>
+      </c>
+      <c r="D183" t="s">
+        <v>59</v>
+      </c>
+      <c r="E183" s="8">
+        <v>550000</v>
+      </c>
+      <c r="F183" s="8"/>
+      <c r="G183" s="8">
+        <v>6660000</v>
+      </c>
+      <c r="H183" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>52</v>
+      </c>
+      <c r="B184" t="s">
+        <v>53</v>
+      </c>
+      <c r="C184" t="s">
+        <v>72</v>
+      </c>
+      <c r="D184" t="s">
+        <v>63</v>
+      </c>
+      <c r="E184" s="8">
+        <v>480000</v>
+      </c>
+      <c r="F184" s="8"/>
+      <c r="G184" s="8">
+        <v>7140000</v>
+      </c>
+      <c r="H184" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>52</v>
+      </c>
+      <c r="B185" t="s">
+        <v>53</v>
+      </c>
+      <c r="C185" t="s">
+        <v>73</v>
+      </c>
+      <c r="D185" t="s">
+        <v>65</v>
+      </c>
+      <c r="E185" s="8">
+        <v>750000</v>
+      </c>
+      <c r="F185" s="8"/>
+      <c r="G185" s="8">
+        <v>7890000</v>
+      </c>
+      <c r="H185" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>75</v>
+      </c>
+      <c r="B186" t="s">
+        <v>53</v>
+      </c>
+      <c r="C186" t="s">
+        <v>78</v>
+      </c>
+      <c r="D186" t="s">
+        <v>79</v>
+      </c>
+      <c r="E186" s="8"/>
+      <c r="F186" s="8">
+        <v>850000</v>
+      </c>
+      <c r="G186" s="8">
+        <v>7040000</v>
+      </c>
+      <c r="H186" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>75</v>
+      </c>
+      <c r="B187" t="s">
+        <v>53</v>
+      </c>
+      <c r="C187" t="s">
+        <v>80</v>
+      </c>
+      <c r="D187" t="s">
+        <v>81</v>
+      </c>
+      <c r="E187" s="8"/>
+      <c r="F187" s="8">
+        <v>550000</v>
+      </c>
+      <c r="G187" s="8">
+        <v>6490000</v>
+      </c>
+      <c r="H187" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>75</v>
+      </c>
+      <c r="B188" t="s">
+        <v>53</v>
+      </c>
+      <c r="C188" t="s">
+        <v>84</v>
+      </c>
+      <c r="D188" t="s">
+        <v>85</v>
+      </c>
+      <c r="E188" s="8"/>
+      <c r="F188" s="8">
+        <v>480000</v>
+      </c>
+      <c r="G188" s="8">
+        <v>6010000</v>
+      </c>
+      <c r="H188" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>75</v>
+      </c>
+      <c r="B189" t="s">
+        <v>53</v>
+      </c>
+      <c r="C189" t="s">
+        <v>86</v>
+      </c>
+      <c r="D189" t="s">
+        <v>87</v>
+      </c>
+      <c r="E189" s="8"/>
+      <c r="F189" s="8">
+        <v>750000</v>
+      </c>
+      <c r="G189" s="8">
+        <v>5260000</v>
+      </c>
+      <c r="H189" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C190" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D190" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E190" s="12">
+        <v>5260000</v>
+      </c>
+      <c r="F190" s="12">
+        <v>2630000</v>
+      </c>
+      <c r="G190" s="12">
+        <v>5260000</v>
+      </c>
+      <c r="H190" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B192" s="4"/>
+      <c r="C192" s="4"/>
+      <c r="D192" s="4"/>
+      <c r="E192" s="4"/>
+      <c r="F192" s="4"/>
+      <c r="G192" s="4"/>
+      <c r="H192" s="4"/>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D193" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E193" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F193" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G193" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H193" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B194" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C194" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D194" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E194" s="7"/>
+      <c r="F194" s="7"/>
+      <c r="G194" s="7">
+        <v>1200000</v>
+      </c>
+      <c r="H194" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>52</v>
+      </c>
+      <c r="B195" t="s">
+        <v>53</v>
+      </c>
+      <c r="C195" t="s">
+        <v>54</v>
+      </c>
+      <c r="D195" t="s">
+        <v>55</v>
+      </c>
+      <c r="E195" s="8">
+        <v>1200000</v>
+      </c>
+      <c r="F195" s="8"/>
+      <c r="G195" s="8">
+        <v>2400000</v>
+      </c>
+      <c r="H195" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>52</v>
+      </c>
+      <c r="B196" t="s">
+        <v>53</v>
+      </c>
+      <c r="C196" t="s">
+        <v>68</v>
+      </c>
+      <c r="D196" t="s">
+        <v>55</v>
+      </c>
+      <c r="E196" s="8">
+        <v>1200000</v>
+      </c>
+      <c r="F196" s="8"/>
+      <c r="G196" s="8">
+        <v>3600000</v>
+      </c>
+      <c r="H196" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>75</v>
+      </c>
+      <c r="B197" t="s">
+        <v>53</v>
+      </c>
+      <c r="C197" t="s">
+        <v>76</v>
+      </c>
+      <c r="D197" t="s">
+        <v>77</v>
+      </c>
+      <c r="E197" s="8"/>
+      <c r="F197" s="8">
+        <v>1200000</v>
+      </c>
+      <c r="G197" s="8">
+        <v>2400000</v>
+      </c>
+      <c r="H197" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C198" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D198" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E198" s="12">
+        <v>2400000</v>
+      </c>
+      <c r="F198" s="12">
+        <v>1200000</v>
+      </c>
+      <c r="G198" s="12">
+        <v>2400000</v>
+      </c>
+      <c r="H198" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B200" s="4"/>
+      <c r="C200" s="4"/>
+      <c r="D200" s="4"/>
+      <c r="E200" s="4"/>
+      <c r="F200" s="4"/>
+      <c r="G200" s="4"/>
+      <c r="H200" s="4"/>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D201" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E201" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F201" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G201" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H201" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A202" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D202" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E202" s="7"/>
+      <c r="F202" s="7"/>
+      <c r="G202" s="7">
+        <v>531250</v>
+      </c>
+      <c r="H202" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>52</v>
+      </c>
+      <c r="B203" t="s">
+        <v>53</v>
+      </c>
+      <c r="C203" t="s">
+        <v>54</v>
+      </c>
+      <c r="D203" t="s">
+        <v>55</v>
+      </c>
+      <c r="E203" s="8">
+        <v>150000</v>
+      </c>
+      <c r="F203" s="8"/>
+      <c r="G203" s="8">
+        <v>681250</v>
+      </c>
+      <c r="H203" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>52</v>
+      </c>
+      <c r="B204" t="s">
+        <v>53</v>
+      </c>
+      <c r="C204" t="s">
+        <v>56</v>
+      </c>
+      <c r="D204" t="s">
+        <v>57</v>
+      </c>
+      <c r="E204" s="8">
+        <v>106250</v>
+      </c>
+      <c r="F204" s="8"/>
+      <c r="G204" s="8">
+        <v>787500</v>
+      </c>
+      <c r="H204" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>52</v>
+      </c>
+      <c r="B205" t="s">
+        <v>53</v>
+      </c>
+      <c r="C205" t="s">
+        <v>58</v>
+      </c>
+      <c r="D205" t="s">
+        <v>59</v>
+      </c>
+      <c r="E205" s="8">
+        <v>68750</v>
+      </c>
+      <c r="F205" s="8"/>
+      <c r="G205" s="8">
+        <v>856250</v>
+      </c>
+      <c r="H205" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>52</v>
+      </c>
+      <c r="B206" t="s">
+        <v>53</v>
+      </c>
+      <c r="C206" t="s">
+        <v>60</v>
+      </c>
+      <c r="D206" t="s">
+        <v>61</v>
+      </c>
+      <c r="E206" s="8">
+        <v>52500</v>
+      </c>
+      <c r="F206" s="8"/>
+      <c r="G206" s="8">
+        <v>908750</v>
+      </c>
+      <c r="H206" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>52</v>
+      </c>
+      <c r="B207" t="s">
+        <v>53</v>
+      </c>
+      <c r="C207" t="s">
+        <v>62</v>
+      </c>
+      <c r="D207" t="s">
+        <v>63</v>
+      </c>
+      <c r="E207" s="8">
+        <v>60000</v>
+      </c>
+      <c r="F207" s="8"/>
+      <c r="G207" s="8">
+        <v>968750</v>
+      </c>
+      <c r="H207" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>52</v>
+      </c>
+      <c r="B208" t="s">
+        <v>53</v>
+      </c>
+      <c r="C208" t="s">
+        <v>64</v>
+      </c>
+      <c r="D208" t="s">
+        <v>65</v>
+      </c>
+      <c r="E208" s="8">
+        <v>93750</v>
+      </c>
+      <c r="F208" s="8"/>
+      <c r="G208" s="8">
+        <v>1062500</v>
+      </c>
+      <c r="H208" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>52</v>
+      </c>
+      <c r="B209" t="s">
+        <v>53</v>
+      </c>
+      <c r="C209" t="s">
+        <v>68</v>
+      </c>
+      <c r="D209" t="s">
+        <v>55</v>
+      </c>
+      <c r="E209" s="8">
+        <v>150000</v>
+      </c>
+      <c r="F209" s="8"/>
+      <c r="G209" s="8">
+        <v>1212500</v>
+      </c>
+      <c r="H209" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>52</v>
+      </c>
+      <c r="B210" t="s">
+        <v>53</v>
+      </c>
+      <c r="C210" t="s">
+        <v>69</v>
+      </c>
+      <c r="D210" t="s">
+        <v>57</v>
+      </c>
+      <c r="E210" s="8">
+        <v>106250</v>
+      </c>
+      <c r="F210" s="8"/>
+      <c r="G210" s="8">
+        <v>1318750</v>
+      </c>
+      <c r="H210" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>52</v>
+      </c>
+      <c r="B211" t="s">
+        <v>53</v>
+      </c>
+      <c r="C211" t="s">
+        <v>70</v>
+      </c>
+      <c r="D211" t="s">
+        <v>59</v>
+      </c>
+      <c r="E211" s="8">
+        <v>68750</v>
+      </c>
+      <c r="F211" s="8"/>
+      <c r="G211" s="8">
+        <v>1387500</v>
+      </c>
+      <c r="H211" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>52</v>
+      </c>
+      <c r="B212" t="s">
+        <v>53</v>
+      </c>
+      <c r="C212" t="s">
+        <v>71</v>
+      </c>
+      <c r="D212" t="s">
+        <v>61</v>
+      </c>
+      <c r="E212" s="8">
+        <v>52500</v>
+      </c>
+      <c r="F212" s="8"/>
+      <c r="G212" s="8">
+        <v>1440000</v>
+      </c>
+      <c r="H212" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>52</v>
+      </c>
+      <c r="B213" t="s">
+        <v>53</v>
+      </c>
+      <c r="C213" t="s">
+        <v>72</v>
+      </c>
+      <c r="D213" t="s">
+        <v>63</v>
+      </c>
+      <c r="E213" s="8">
+        <v>60000</v>
+      </c>
+      <c r="F213" s="8"/>
+      <c r="G213" s="8">
+        <v>1500000</v>
+      </c>
+      <c r="H213" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>52</v>
+      </c>
+      <c r="B214" t="s">
+        <v>53</v>
+      </c>
+      <c r="C214" t="s">
+        <v>73</v>
+      </c>
+      <c r="D214" t="s">
+        <v>65</v>
+      </c>
+      <c r="E214" s="8">
+        <v>93750</v>
+      </c>
+      <c r="F214" s="8"/>
+      <c r="G214" s="8">
+        <v>1593750</v>
+      </c>
+      <c r="H214" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>75</v>
+      </c>
+      <c r="B215" t="s">
+        <v>53</v>
+      </c>
+      <c r="C215" t="s">
+        <v>76</v>
+      </c>
+      <c r="D215" t="s">
+        <v>77</v>
+      </c>
+      <c r="E215" s="8"/>
+      <c r="F215" s="8">
+        <v>150000</v>
+      </c>
+      <c r="G215" s="8">
+        <v>1443750</v>
+      </c>
+      <c r="H215" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>75</v>
+      </c>
+      <c r="B216" t="s">
+        <v>53</v>
+      </c>
+      <c r="C216" t="s">
+        <v>78</v>
+      </c>
+      <c r="D216" t="s">
+        <v>79</v>
+      </c>
+      <c r="E216" s="8"/>
+      <c r="F216" s="8">
+        <v>106250</v>
+      </c>
+      <c r="G216" s="8">
+        <v>1337500</v>
+      </c>
+      <c r="H216" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>75</v>
+      </c>
+      <c r="B217" t="s">
+        <v>53</v>
+      </c>
+      <c r="C217" t="s">
+        <v>80</v>
+      </c>
+      <c r="D217" t="s">
+        <v>81</v>
+      </c>
+      <c r="E217" s="8"/>
+      <c r="F217" s="8">
+        <v>68750</v>
+      </c>
+      <c r="G217" s="8">
+        <v>1268750</v>
+      </c>
+      <c r="H217" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>75</v>
+      </c>
+      <c r="B218" t="s">
+        <v>53</v>
+      </c>
+      <c r="C218" t="s">
+        <v>82</v>
+      </c>
+      <c r="D218" t="s">
+        <v>83</v>
+      </c>
+      <c r="E218" s="8"/>
+      <c r="F218" s="8">
+        <v>52500</v>
+      </c>
+      <c r="G218" s="8">
+        <v>1216250</v>
+      </c>
+      <c r="H218" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>75</v>
+      </c>
+      <c r="B219" t="s">
+        <v>53</v>
+      </c>
+      <c r="C219" t="s">
+        <v>84</v>
+      </c>
+      <c r="D219" t="s">
+        <v>85</v>
+      </c>
+      <c r="E219" s="8"/>
+      <c r="F219" s="8">
+        <v>60000</v>
+      </c>
+      <c r="G219" s="8">
+        <v>1156250</v>
+      </c>
+      <c r="H219" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>75</v>
+      </c>
+      <c r="B220" t="s">
+        <v>53</v>
+      </c>
+      <c r="C220" t="s">
+        <v>86</v>
+      </c>
+      <c r="D220" t="s">
+        <v>87</v>
+      </c>
+      <c r="E220" s="8"/>
+      <c r="F220" s="8">
+        <v>93750</v>
+      </c>
+      <c r="G220" s="8">
+        <v>1062500</v>
+      </c>
+      <c r="H220" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A221" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B221" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C221" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D221" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E221" s="12">
+        <v>1062500</v>
+      </c>
+      <c r="F221" s="12">
+        <v>531250</v>
+      </c>
+      <c r="G221" s="12">
+        <v>1062500</v>
+      </c>
+      <c r="H221" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A223" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B223" s="4"/>
+      <c r="C223" s="4"/>
+      <c r="D223" s="4"/>
+      <c r="E223" s="4"/>
+      <c r="F223" s="4"/>
+      <c r="G223" s="4"/>
+      <c r="H223" s="4"/>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A224" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C224" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D224" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E224" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F224" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G224" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H224" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A225" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B225" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C225" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D225" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E225" s="7"/>
+      <c r="F225" s="7"/>
+      <c r="G225" s="7">
+        <v>-3140000</v>
+      </c>
+      <c r="H225" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>24</v>
+      </c>
+      <c r="B226" t="s">
+        <v>17</v>
+      </c>
+      <c r="C226" t="s">
+        <v>25</v>
+      </c>
+      <c r="D226" t="s">
+        <v>26</v>
+      </c>
+      <c r="E226" s="8"/>
+      <c r="F226" s="8">
+        <v>490000</v>
+      </c>
+      <c r="G226" s="8">
+        <v>-3630000</v>
+      </c>
+      <c r="H226" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>30</v>
+      </c>
+      <c r="B227" t="s">
+        <v>17</v>
+      </c>
+      <c r="C227" t="s">
+        <v>31</v>
+      </c>
+      <c r="D227" t="s">
+        <v>32</v>
+      </c>
+      <c r="E227" s="8"/>
+      <c r="F227" s="8">
+        <v>784000</v>
+      </c>
+      <c r="G227" s="8">
+        <v>-4414000</v>
+      </c>
+      <c r="H227" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B228" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C228" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D228" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E228" s="12">
+        <v>0</v>
+      </c>
+      <c r="F228" s="12">
+        <v>1274000</v>
+      </c>
+      <c r="G228" s="12">
+        <v>-4414000</v>
+      </c>
+      <c r="H228" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A230" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B230" s="4"/>
+      <c r="C230" s="4"/>
+      <c r="D230" s="4"/>
+      <c r="E230" s="4"/>
+      <c r="F230" s="4"/>
+      <c r="G230" s="4"/>
+      <c r="H230" s="4"/>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A231" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C231" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D231" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E231" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F231" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G231" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H231" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>16</v>
+      </c>
+      <c r="B232" t="s">
+        <v>17</v>
+      </c>
+      <c r="C232" t="s">
+        <v>18</v>
+      </c>
+      <c r="D232" t="s">
+        <v>19</v>
+      </c>
+      <c r="E232" s="8"/>
+      <c r="F232" s="8">
+        <v>900000</v>
+      </c>
+      <c r="G232" s="8">
+        <v>-900000</v>
+      </c>
+      <c r="H232" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>20</v>
+      </c>
+      <c r="B233" t="s">
+        <v>17</v>
+      </c>
+      <c r="C233" t="s">
+        <v>21</v>
+      </c>
+      <c r="D233" t="s">
+        <v>22</v>
+      </c>
+      <c r="E233" s="8"/>
+      <c r="F233" s="8">
         <v>375000</v>
       </c>
-      <c r="G98" s="8">
+      <c r="G233" s="8">
         <v>-1275000</v>
       </c>
-      <c r="H98" t="s">
+      <c r="H233" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
         <v>27</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B234" t="s">
         <v>17</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C234" t="s">
         <v>28</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D234" t="s">
         <v>29</v>
       </c>
-      <c r="E99" s="8"/>
-      <c r="F99" s="8">
+      <c r="E234" s="8"/>
+      <c r="F234" s="8">
         <v>730000</v>
       </c>
-      <c r="G99" s="8">
+      <c r="G234" s="8">
         <v>-2005000</v>
       </c>
-      <c r="H99" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C100" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D100" s="11" t="s">
+      <c r="H234" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A235" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B235" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C235" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D235" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E100" s="12">
+      <c r="E235" s="12">
         <v>0</v>
       </c>
-      <c r="F100" s="12">
+      <c r="F235" s="12">
         <v>2005000</v>
       </c>
-      <c r="G100" s="12">
+      <c r="G235" s="12">
         <v>-2005000</v>
       </c>
-      <c r="H100" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" s="13" t="s">
-        <v>84</v>
+      <c r="H235" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A237" s="13" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="24">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="A56:H56"/>
-    <mergeCell ref="A62:H62"/>
-    <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A73:H73"/>
-    <mergeCell ref="A78:H78"/>
-    <mergeCell ref="A83:H83"/>
-    <mergeCell ref="A88:H88"/>
-    <mergeCell ref="A95:H95"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="A91:H91"/>
+    <mergeCell ref="A101:H101"/>
+    <mergeCell ref="A110:H110"/>
+    <mergeCell ref="A122:H122"/>
+    <mergeCell ref="A130:H130"/>
+    <mergeCell ref="A135:H135"/>
+    <mergeCell ref="A141:H141"/>
+    <mergeCell ref="A146:H146"/>
+    <mergeCell ref="A152:H152"/>
+    <mergeCell ref="A157:H157"/>
+    <mergeCell ref="A162:H162"/>
+    <mergeCell ref="A167:H167"/>
+    <mergeCell ref="A175:H175"/>
+    <mergeCell ref="A192:H192"/>
+    <mergeCell ref="A200:H200"/>
+    <mergeCell ref="A223:H223"/>
+    <mergeCell ref="A230:H230"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
